--- a/storage/src/main/resources/excel/orderGroup.xlsx
+++ b/storage/src/main/resources/excel/orderGroup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\hml\hml-server\storage\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335A5EDF-D6DA-4697-ABFB-C11D7454AC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF46B48-4FB9-4662-986C-ACCA2DE2AF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>客户名称</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -111,6 +111,27 @@
   </si>
   <si>
     <t>{.createTime}</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>{.item}</t>
+  </si>
+  <si>
+    <t>{.inStorageCount}</t>
+  </si>
+  <si>
+    <t>{.remainCount}</t>
+  </si>
+  <si>
+    <t>ITEM号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>入库数量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>余量</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -233,7 +254,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -249,17 +270,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -547,22 +571,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
       <c r="Q1" s="3"/>
@@ -605,40 +629,58 @@
       <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
+      <c r="L2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3" spans="1:21" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>22</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.3">
@@ -655,7 +697,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
